--- a/daily/2026-04-14.xlsx
+++ b/daily/2026-04-14.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1440,7 +1458,7 @@
         <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>9</v>
@@ -4471,583 +4489,1325 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Miller scored 23 pts vs 20.5 line (+2.5), UNDER missed by 2.5 pts. Miller played 37 min (+5.3 vs L10 avg of 31.5) — 17% more than expected. Shooting efficiency was hot: 52.9% FG (+7.2% vs L10 avg of 45.7%). 9/17 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 19.4 pts — actual 23 was 3.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 5 pts vs 5.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 18 played vs L10 avg 20.5. Shooting efficiency was cold: 25.0% FG (-19.3% vs L10 avg of 44.3%). 2/8 from the field. Counter-signals that proved correct: Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.5 pts — actual 5 was 2.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Norman Powell</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 11 pts vs 17.5 line (-6.5), UNDER hit by 6.5 pts. Powell played 19 min (-6.5 vs L10 avg of 25.8) — 25% less than expected. Shooting efficiency was hot: 55.6% FG (+12.7% vs L10 avg of 42.9%). 5/9 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.4 pts — actual 11 was 4.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Powell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>WIN — White scored 19 pts vs 12.5 line (+6.5), OVER hit by 6.5 pts. White played 26 min (+6.8 vs L10 avg of 18.8) — 36% more than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 49.1%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 14.8 pts — actual 19 was 4.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ball scored 30 pts vs 22.5 line (+7.5), OVER hit by 7.5 pts. Ball played 40 min (+8.8 vs L10 avg of 31.2) — 28% more than expected. Shooting was in line with averages: 38.7% FG (12/31, L10 avg 41.4%). Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.4 pts — actual 30 was 7.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Ball's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wiggins scored 27 pts vs 14.5 line (+12.5), OVER hit by 12.5 pts. Wiggins played 42 min (+14.1 vs L10 avg of 27.8) — 51% more than expected. Shooting efficiency was hot: 55.6% FG (+8.2% vs L10 avg of 47.4%). 10/18 from the field. Signals that called it correctly: Volume, Context, H2H (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 20.4 pts — actual 27 was 6.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wiggins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 28 pts vs 8.5 line (+19.5), OVER hit by 19.5 pts. Mitchell played 48 min (+17.9 vs L10 avg of 29.6) — 60% more than expected. Shooting was in line with averages: 50.0% FG (12/24, L10 avg 53.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Pace. Projection model targeted 10.6 pts — actual 28 was 17.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 28 pts vs 15.5 line (+12.5), UNDER missed by 12.5 pts. Bridges played 44 min (+15.5 vs L10 avg of 28.0) — 55% more than expected. Shooting was in line with averages: 55.6% FG (10/18, L10 avg 53.1%). Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.4 pts — actual 28 was 13.6 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when CHA is involved.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Diabaté scored 8 pts vs 8.5 line (-0.5), UNDER hit by 0.5 pts. Diabaté played 36 min (+9.7 vs L10 avg of 26.4) — 37% more than expected. Shooting efficiency was hot: 80.0% FG (+9.0% vs L10 avg of 71.0%). 4/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 6.9 pts — actual 8 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Diabaté in this role.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Knueppel scored 6 pts vs 18.5 line (-12.5), OVER missed by 12.5 pts. Minutes were as expected: 34 played vs L10 avg 31.9. Shooting efficiency was cold: 16.7% FG (-22.8% vs L10 avg of 39.5%). 2/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 20.9 pts — actual 6 was 14.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Larsson scored 6 pts vs 9.5 line (-3.5), OVER missed by 3.5 pts. Larsson played 22 min (-8.4 vs L10 avg of 30.2) — 28% less than expected. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 50.2%). Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.3 pts — actual 6 was 8.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Larsson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 13 pts vs 11.5 line (+1.5), OVER hit by 1.5 pts. Jr. played 41 min (+13.6 vs L10 avg of 27.2) — 50% more than expected. Shooting efficiency was cold: 35.7% FG (-19.4% vs L10 avg of 55.1%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 14.9 pts — actual 13 was 1.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Adebayo scored 6 pts vs 20.5 line (-14.5), OVER missed by 14.5 pts. Adebayo played 11 min (-22.9 vs L10 avg of 34.3) — 67% less than expected. Shooting efficiency was hot: 100.0% FG (+57.6% vs L10 avg of 42.4%). 3/3 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 21.1 pts — actual 6 was 15.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Adebayo for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Ryan Kalkbrenner</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>3.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kalkbrenner scored 6 pts vs 3.5 line (+2.5), OVER hit by 2.5 pts. Kalkbrenner played 13 min (-6.0 vs L10 avg of 18.9) — 32% less than expected. Shooting efficiency was cold: 75.0% FG (-16.8% vs L10 avg of 91.8%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (7/10 aligned). Counter-signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 5.7 pts — actual 6 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Kalkbrenner in this role.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>MIA @ CHA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Herro scored 23 pts vs 21.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 32.6. Shooting efficiency was cold: 38.9% FG (-6.9% vs L10 avg of 45.8%). 7/18 from the field. Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.8 pts — actual 23 was 4.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 22 pts vs 26.5 line (-4.5), OVER missed by 4.5 pts. Booker played 38 min (+4.0 vs L10 avg of 33.6) — 12% more than expected. Shooting efficiency was cold: 41.2% FG (-5.5% vs L10 avg of 46.7%). 7/17 from the field. Counter-signals that proved correct: HR L10, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 27.3 pts — actual 22 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Avdija scored 41 pts vs 24.5 line (+16.5), UNDER missed by 16.5 pts. Avdija played 38 min (+5.4 vs L10 avg of 32.8) — 16% more than expected. Shooting efficiency was hot: 68.2% FG (+19.3% vs L10 avg of 48.9%). 15/22 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 18.2 pts — actual 41 was 22.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brooks scored 20 pts vs 17.5 line (+2.5), UNDER missed by 2.5 pts. Brooks played 37 min (+9.7 vs L10 avg of 26.9) — 36% more than expected. Shooting efficiency was hot: 60.0% FG (+21.1% vs L10 avg of 38.9%). 6/10 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, H2H. Projection model targeted 16.8 pts — actual 20 was 3.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 35 pts vs 17.5 line (+17.5), UNDER missed by 17.5 pts. Green played 39 min (+12.0 vs L10 avg of 26.7) — 45% more than expected. Shooting efficiency was hot: 48.3% FG (+5.1% vs L10 avg of 43.2%). 14/29 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 13.9 pts — actual 35 was 21.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 21 pts vs 16.5 line (+4.5), UNDER missed by 4.5 pts. Holiday played 38 min (+7.0 vs L10 avg of 31.4) — 22% more than expected. Shooting efficiency was cold: 38.9% FG (-5.3% vs L10 avg of 44.2%). 7/18 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 12.7 pts — actual 21 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 2 pts vs 13.5 line (-11.5), UNDER hit by 11.5 pts. Minutes were as expected: 29 played vs L10 avg 26.3. Shooting efficiency was cold: 16.7% FG (-31.4% vs L10 avg of 48.1%). 1/6 from the field. Signals that called it correctly: HR L10, Trend, Context, H2H, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 12.0 pts — actual 2 was 10.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Clingan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 8 pts vs 13.5 line (-5.5), OVER missed by 5.5 pts. Camara played 36 min (+3.1 vs L10 avg of 33.2) — 9% more than expected. Shooting efficiency was cold: 33.3% FG (-16.7% vs L10 avg of 50.0%). 3/9 from the field. Counter-signals that proved correct: HR L30, Defense, H2H, Pace. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 15.4 pts — actual 8 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Henderson scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Henderson played 17 min (-10.4 vs L10 avg of 27.6) — 38% less than expected. Shooting efficiency was hot: 50.0% FG (+6.4% vs L10 avg of 43.6%). 3/6 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.0 pts — actual 9 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Henderson in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Mark Williams</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 22 played vs L10 avg 21.3. Shooting efficiency was hot: 66.7% FG (+10.1% vs L10 avg of 56.6%). 2/3 from the field. Signals that called it correctly: HR L10, Context, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Trend. Projection model targeted 9.9 pts — actual 4 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Williams's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Jordan Goodwin</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E27" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Goodwin scored 12 pts vs 7.5 line (+4.5), OVER hit by 4.5 pts. Goodwin played 29 min (+5.3 vs L10 avg of 23.3) — 23% more than expected. Shooting efficiency was hot: 57.1% FG (+9.2% vs L10 avg of 47.9%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, Min Trend. Projection model targeted 9.7 pts — actual 12 was 2.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN — O'Neale scored 7 pts vs 6.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 23.5. Shooting efficiency was hot: 60.0% FG (+13.0% vs L10 avg of 47.0%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, Pace, Min Trend. Projection model targeted 7.1 pts — actual 7 was 0.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for O'Neale in this role.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — III scored 2 pts vs 5.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 16 played vs L10 avg 17.5. Shooting efficiency was cold: 16.7% FG (-50.5% vs L10 avg of 67.2%). 1/6 from the field. Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.6 pts — actual 2 was 5.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Oso Ighodaro</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>POR @ PHX</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ighodaro scored 3 pts vs 4.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 23 played vs L10 avg 24.0. Shooting efficiency was cold: 50.0% FG (-23.3% vs L10 avg of 73.3%). 1/2 from the field. Counter-signals that proved correct: Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.4 pts — actual 3 was 5.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:37</t>
+        </is>
       </c>
     </row>
   </sheetData>
